--- a/reference/samples/08_Document_Checklist.xlsx
+++ b/reference/samples/08_Document_Checklist.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="39">
   <si>
     <t xml:space="preserve">Document Checklist Export — รอบบัญชี มิถุนายน 2569</t>
   </si>
   <si>
-    <t xml:space="preserve">อ้างอิง: ไฟล์ 34-accounting-document-checklist-exceptions.md — จัดทำโดย นันทพร (บัญชี) วันที่ 05/07/2569</t>
+    <t xml:space="preserve">จัดทำโดย นันทพร (บัญชี) วันที่ 05/07/2569</t>
   </si>
   <si>
     <t xml:space="preserve">source_type</t>
@@ -121,7 +121,22 @@
     <t xml:space="preserve">ขาดเอกสาร (Critical)</t>
   </si>
   <si>
-    <t xml:space="preserve">หมายเหตุ: ห้าม Export Accounting Pack ถ้ายังมีรายการ Critical เปิดอยู่ (ไฟล์ 30 Readiness Check)</t>
+    <t xml:space="preserve">หมายเหตุ: ห้าม Export Accounting Pack ถ้ายังมีรายการ Critical เปิดอยู่ (Readiness Check)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">expense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXP-2569-0351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">อนุญาตปิดงวด — ยังรอเอกสาร</t>
+  </si>
+  <si>
+    <t xml:space="preserve">รอใบเสร็จค่าที่พักฉบับจริง (อนุญาตปิดงวด: ผู้บริหารอนุญาตปิดงวด เอกสารตามมาเดือนหน้า)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ประยุทธ์ บุญมี</t>
   </si>
 </sst>
 </file>
@@ -601,7 +616,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
@@ -772,40 +787,69 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="8" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="8" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="9" t="n">
-        <f aca="false">COUNTIF(C5:C10,"ครบถ้วน")</f>
-        <v>3</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="B14" s="9" t="n">
-        <f aca="false">COUNTIF(C5:C10,"ขาดเอกสาร")</f>
-        <v>1</v>
+        <f aca="false">COUNTIF(C5:C11,"ครบถ้วน")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="9" t="n">
+        <f aca="false">COUNTIF(C5:C11,"ขาดเอกสาร")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="9" t="n">
-        <f aca="false">COUNTIF(C5:C10,"รอตรวจสอบ")</f>
+      <c r="B16" s="9" t="n">
+        <f aca="false">COUNTIF(C5:C11,"รอตรวจสอบ")</f>
         <v>2</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="9" t="n">
+        <f aca="false">COUNTIF(C5:C11,"อนุญาตปิดงวด — ยังรอเอกสาร")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="10" t="s">
         <v>33</v>
       </c>
     </row>
